--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487491_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487491_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6402</v>
+        <v>2.3674</v>
       </c>
       <c r="E2" t="n">
-        <v>1.2868</v>
+        <v>0.4417</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3533</v>
+        <v>1.9257</v>
       </c>
       <c r="G2" t="n">
         <v>0.7982</v>
@@ -610,13 +610,13 @@
         <v>2.3502</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4503</v>
+        <v>1.1774</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9228</v>
+        <v>0.0776</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5275</v>
+        <v>1.0998</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4808</v>
+        <v>-0.6389</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2025</v>
+        <v>-1.2687</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6833</v>
+        <v>0.6298</v>
       </c>
       <c r="G3" t="n">
         <v>-0.3846</v>
@@ -688,13 +688,13 @@
         <v>0.9792</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7236</v>
+        <v>-0.3961</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0369</v>
+        <v>-0.0294</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3132</v>
+        <v>-0.3667</v>
       </c>
       <c r="V3" t="n">
         <v>2.1003</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.8548</v>
+        <v>-0.8313</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.9473</v>
+        <v>-1.6832</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0925</v>
+        <v>0.8519</v>
       </c>
       <c r="G4" t="n">
         <v>-1.8165</v>
@@ -766,13 +766,13 @@
         <v>1.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2133</v>
+        <v>-0.1898</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.31</v>
+        <v>-0.0459</v>
       </c>
       <c r="U4" t="n">
-        <v>0.09660000000000001</v>
+        <v>-0.1439</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. AÑON DOSIL</t>
+          <t>J. MARTINEZ FERREIRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.1025</v>
+        <v>-0.9495</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3788</v>
+        <v>0.26</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7238</v>
+        <v>-1.2095</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0115</v>
+        <v>0.4996</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3526</v>
+        <v>-0.8445</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.3641</v>
+        <v>1.3441</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4302</v>
+        <v>0.6923</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1432</v>
+        <v>-0.6414</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.713</v>
+        <v>1.3337</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4417</v>
+        <v>-0.1927</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2094</v>
+        <v>-0.2031</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6511</v>
+        <v>0.0104</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5668</v>
+        <v>0.7834</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.546</v>
+        <v>0.7834</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.167</v>
+        <v>-0.7405</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3229</v>
+        <v>-0.4323</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1559</v>
+        <v>-0.3082</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.4908</v>
+        <v>-1.492</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4931</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.9839</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MARTINEZ FERREIRO</t>
+          <t>A. AÑON DOSIL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1587</v>
+        <v>-1.129</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1577</v>
+        <v>-0.4052</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3164</v>
+        <v>-0.7238</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4996</v>
+        <v>-0.0115</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8445</v>
+        <v>1.3526</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3441</v>
+        <v>-1.3641</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6923</v>
+        <v>0.4302</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6414</v>
+        <v>1.1432</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3337</v>
+        <v>-0.713</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1927</v>
+        <v>-0.4417</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2031</v>
+        <v>0.2094</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0104</v>
+        <v>-0.6511</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7834</v>
+        <v>1.5668</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7834</v>
+        <v>2.546</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9497</v>
+        <v>-0.1935</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5346</v>
+        <v>-0.3494</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4151</v>
+        <v>0.1559</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.492</v>
+        <v>-2.4908</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.4931</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.492</v>
+        <v>-2.9839</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. ESPINOZA OROZCO</t>
+          <t>D. WILLIAM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.3938</v>
+        <v>-1.5299</v>
       </c>
       <c r="E7" t="n">
-        <v>-6.1179</v>
+        <v>-3.6237</v>
       </c>
       <c r="F7" t="n">
-        <v>3.7241</v>
+        <v>2.0939</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7803</v>
+        <v>0.3111</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1181</v>
+        <v>-0.6533</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6622</v>
+        <v>0.9644</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.5614</v>
+        <v>-0.5397999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7368</v>
+        <v>-0.9324</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.8246</v>
+        <v>0.3927</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7811</v>
+        <v>0.8509</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6187</v>
+        <v>0.2791</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1624</v>
+        <v>0.5717</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1958</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>-2.9377</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7419</v>
+        <v>2.9377</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1435</v>
+        <v>-0.2914</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6199</v>
+        <v>-0.697</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4765</v>
+        <v>0.4055</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2742</v>
+        <v>-1.5495</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.9988</v>
+        <v>0.5507</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2754</v>
+        <v>-2.1003</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. WILLIAM</t>
+          <t>R. ESPINOZA OROZCO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.2509</v>
+        <v>-1.9262</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.9706</v>
+        <v>-5.8374</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7196</v>
+        <v>3.9112</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3111</v>
+        <v>-0.7803</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6533</v>
+        <v>-0.1181</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9644</v>
+        <v>-0.6622</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5397999999999999</v>
+        <v>-1.5614</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9324</v>
+        <v>-0.7368</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3927</v>
+        <v>-0.8246</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8509</v>
+        <v>0.7811</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2791</v>
+        <v>0.6187</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5717</v>
+        <v>0.1624</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q8" t="n">
         <v>-2.9377</v>
       </c>
       <c r="R8" t="n">
-        <v>2.9377</v>
+        <v>2.7419</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.0125</v>
+        <v>0.3242</v>
       </c>
       <c r="T8" t="n">
-        <v>-2.0438</v>
+        <v>-0.3394</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0313</v>
+        <v>0.6636</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.5495</v>
+        <v>-1.2742</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5507</v>
+        <v>-0.9988</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.1003</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.0824</v>
+        <v>-4.1938</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.3454</v>
+        <v>-5.5102</v>
       </c>
       <c r="F9" t="n">
-        <v>1.263</v>
+        <v>1.3165</v>
       </c>
       <c r="G9" t="n">
         <v>-5.0738</v>
@@ -1156,13 +1156,13 @@
         <v>2.1543</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9083</v>
+        <v>-0.0197</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.3486</v>
+        <v>-0.5134</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4403</v>
+        <v>0.4937</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2754</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-9.722099999999999</v>
+        <v>-8.831200000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-18.518</v>
+        <v>-17.6267</v>
       </c>
       <c r="F10" t="n">
-        <v>8.7956</v>
+        <v>8.7957</v>
       </c>
       <c r="G10" t="n">
         <v>-6.457800000000001</v>
@@ -1204,13 +1204,13 @@
         <v>-1.7081</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.7496</v>
+        <v>-4.749600000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-7.6968</v>
+        <v>-7.696800000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.765300000000001</v>
+        <v>-2.7653</v>
       </c>
       <c r="L10" t="n">
         <v>-4.9312</v>
@@ -1234,19 +1234,19 @@
         <v>15.6678</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.220400000000001</v>
+        <v>-0.3294</v>
       </c>
       <c r="T10" t="n">
-        <v>-3.220100000000001</v>
+        <v>-2.3292</v>
       </c>
       <c r="U10" t="n">
-        <v>1.9998</v>
+        <v>1.9997</v>
       </c>
       <c r="V10" t="n">
         <v>-4.9816</v>
       </c>
       <c r="W10" t="n">
-        <v>5.129199999999999</v>
+        <v>5.1292</v>
       </c>
       <c r="X10" t="n">
         <v>-10.111</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>7.3264</v>
+        <v>8.133900000000001</v>
       </c>
       <c r="E11" t="n">
         <v>2.5647</v>
       </c>
       <c r="F11" t="n">
-        <v>4.7617</v>
+        <v>5.5692</v>
       </c>
       <c r="G11" t="n">
         <v>5.83</v>
@@ -1312,13 +1312,13 @@
         <v>1.9585</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0739</v>
+        <v>-0.2664</v>
       </c>
       <c r="T11" t="n">
         <v>-0.7258</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3482</v>
+        <v>0.4593</v>
       </c>
       <c r="V11" t="n">
         <v>2.7662</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. LUIS</t>
+          <t>C. IGLESIAS GONZALEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.2795</v>
+        <v>4.2728</v>
       </c>
       <c r="E12" t="n">
-        <v>2.7201</v>
+        <v>-0.1352</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5594</v>
+        <v>4.408</v>
       </c>
       <c r="G12" t="n">
-        <v>2.3721</v>
+        <v>0.416</v>
       </c>
       <c r="H12" t="n">
-        <v>3.4737</v>
+        <v>1.2399</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.1016</v>
+        <v>-0.8239</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9326</v>
+        <v>-1.1796</v>
       </c>
       <c r="K12" t="n">
-        <v>2.8581</v>
+        <v>0.8931</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.9255</v>
+        <v>-2.0727</v>
       </c>
       <c r="M12" t="n">
-        <v>1.4394</v>
+        <v>1.5956</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6156</v>
+        <v>0.3468</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8239</v>
+        <v>1.2488</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5875</v>
+        <v>0.3917</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.1958</v>
+        <v>-1.9585</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7834</v>
+        <v>2.3502</v>
       </c>
       <c r="S12" t="n">
-        <v>3.0871</v>
+        <v>-0.1272</v>
       </c>
       <c r="T12" t="n">
-        <v>1.7079</v>
+        <v>-0.5893</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3792</v>
+        <v>0.4621</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.7673</v>
+        <v>3.5922</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2754</v>
+        <v>3.5922</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.0427</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. IGLESIAS GONZALEZ</t>
+          <t>J. LUIS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.7268</v>
+        <v>2.4542</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.9539</v>
+        <v>1.6967</v>
       </c>
       <c r="F13" t="n">
-        <v>3.6806</v>
+        <v>0.7574</v>
       </c>
       <c r="G13" t="n">
-        <v>0.416</v>
+        <v>2.3721</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2399</v>
+        <v>3.4737</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8239</v>
+        <v>-1.1016</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.1796</v>
+        <v>0.9326</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8931</v>
+        <v>2.8581</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.0727</v>
+        <v>-1.9255</v>
       </c>
       <c r="M13" t="n">
-        <v>1.5956</v>
+        <v>1.4394</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3468</v>
+        <v>0.6156</v>
       </c>
       <c r="O13" t="n">
-        <v>1.2488</v>
+        <v>0.8239</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3917</v>
+        <v>0.5875</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9585</v>
+        <v>-0.1958</v>
       </c>
       <c r="R13" t="n">
-        <v>2.3502</v>
+        <v>0.7834</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.6732</v>
+        <v>1.2618</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.408</v>
+        <v>0.6846</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2652</v>
+        <v>0.5773</v>
       </c>
       <c r="V13" t="n">
-        <v>3.5922</v>
+        <v>-1.7673</v>
       </c>
       <c r="W13" t="n">
-        <v>3.5922</v>
+        <v>0.2754</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-2.0427</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7378</v>
+        <v>1.4844</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.2828</v>
+        <v>-2.1805</v>
       </c>
       <c r="F14" t="n">
-        <v>3.0206</v>
+        <v>3.6649</v>
       </c>
       <c r="G14" t="n">
         <v>0.1871</v>
@@ -1546,13 +1546,13 @@
         <v>1.5668</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6647999999999999</v>
+        <v>0.0819</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0465</v>
+        <v>0.1488</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7112000000000001</v>
+        <v>-0.0669</v>
       </c>
       <c r="V14" t="n">
         <v>1.6071</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. FERNANDEZ GIL</t>
+          <t>E. CZERAPOWIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3147</v>
+        <v>0.926</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.8772</v>
+        <v>-1.1855</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5625</v>
+        <v>2.1114</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0502</v>
+        <v>1.5564</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.49</v>
+        <v>0.1471</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4397</v>
+        <v>1.4093</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.3021</v>
+        <v>0.9795</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.3118</v>
+        <v>-0.131</v>
       </c>
       <c r="L15" t="n">
-        <v>0.009599999999999999</v>
+        <v>1.1105</v>
       </c>
       <c r="M15" t="n">
-        <v>1.2519</v>
+        <v>0.5769</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8218</v>
+        <v>0.2781</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4301</v>
+        <v>0.2988</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.7834</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1543</v>
+        <v>-1.9585</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3709</v>
+        <v>1.9585</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6401</v>
+        <v>0.5286</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.188</v>
+        <v>-0.2064</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5479000000000001</v>
+        <v>0.735</v>
       </c>
       <c r="V15" t="n">
-        <v>1.159</v>
+        <v>-1.159</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7673</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6083</v>
+        <v>-1.159</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. CZERAPOWIC</t>
+          <t>M. FERNANDEZ GIL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3675</v>
+        <v>0.1537</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.2088</v>
+        <v>-2.4678</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8413</v>
+        <v>2.6215</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5564</v>
+        <v>-0.0502</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1471</v>
+        <v>-0.49</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4093</v>
+        <v>0.4397</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9795</v>
+        <v>-1.3021</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.131</v>
+        <v>-1.3118</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1105</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5769</v>
+        <v>1.2519</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2781</v>
+        <v>0.8218</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2988</v>
+        <v>0.4301</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9585</v>
+        <v>-2.1543</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9585</v>
+        <v>1.3709</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7649</v>
+        <v>-0.1717</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2298</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4649</v>
+        <v>0.607</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.159</v>
+        <v>1.159</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.7673</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.159</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7094</v>
+        <v>-0.8329</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.7867</v>
+        <v>-3.8891</v>
       </c>
       <c r="F17" t="n">
-        <v>3.0773</v>
+        <v>3.0562</v>
       </c>
       <c r="G17" t="n">
         <v>-0.5502</v>
@@ -1780,13 +1780,13 @@
         <v>1.3709</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3868</v>
+        <v>0.2633</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.7863</v>
       </c>
       <c r="U17" t="n">
-        <v>1.0708</v>
+        <v>1.0497</v>
       </c>
       <c r="V17" t="n">
         <v>1.2166</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.8152</v>
+        <v>-1.9129</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0217</v>
+        <v>-0.183</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8369</v>
+        <v>-1.73</v>
       </c>
       <c r="G18" t="n">
         <v>-0.4081</v>
@@ -1858,13 +1858,13 @@
         <v>0.5875</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2013</v>
+        <v>0.1035</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2664</v>
+        <v>0.0618</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.0418</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2166</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1415</v>
+        <v>-3.5925</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9928</v>
+        <v>-3.0161</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1487</v>
+        <v>-0.5764</v>
       </c>
       <c r="G19" t="n">
         <v>-2.8952</v>
@@ -1936,13 +1936,13 @@
         <v>0.7834</v>
       </c>
       <c r="S19" t="n">
-        <v>2.3621</v>
+        <v>0.911</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2151</v>
+        <v>0.1917</v>
       </c>
       <c r="U19" t="n">
-        <v>1.147</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2166</v>
@@ -1969,16 +1969,16 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>9.722199999999999</v>
+        <v>11.0867</v>
       </c>
       <c r="E20" t="n">
-        <v>-8.7957</v>
+        <v>-8.7958</v>
       </c>
       <c r="F20" t="n">
-        <v>18.5178</v>
+        <v>19.8822</v>
       </c>
       <c r="G20" t="n">
-        <v>6.4579</v>
+        <v>6.457900000000001</v>
       </c>
       <c r="H20" t="n">
         <v>1.7082</v>
@@ -1996,10 +1996,10 @@
         <v>-0.1818</v>
       </c>
       <c r="M20" t="n">
-        <v>7.696599999999999</v>
+        <v>7.696600000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>2.7653</v>
+        <v>2.765299999999999</v>
       </c>
       <c r="O20" t="n">
         <v>4.9314</v>
@@ -2014,13 +2014,13 @@
         <v>12.7301</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2204</v>
+        <v>2.5848</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.9997</v>
+        <v>-1.9996</v>
       </c>
       <c r="U20" t="n">
-        <v>3.22</v>
+        <v>4.5846</v>
       </c>
       <c r="V20" t="n">
         <v>4.9816</v>
